--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128534131</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128533836</v>
       </c>
       <c r="B6" t="n">
-        <v>91225</v>
+        <v>91231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>128533911</v>
       </c>
       <c r="B7" t="n">
-        <v>92770</v>
+        <v>92776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128533836</v>
       </c>
       <c r="B6" t="n">
-        <v>91231</v>
+        <v>91237</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>128533911</v>
       </c>
       <c r="B7" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128533836</v>
       </c>
       <c r="B6" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>128533911</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128534131</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128533836</v>
       </c>
       <c r="B6" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>128533911</v>
       </c>
       <c r="B7" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128533836</v>
       </c>
       <c r="B6" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>128533911</v>
       </c>
       <c r="B7" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128533836</v>
       </c>
       <c r="B6" t="n">
-        <v>91272</v>
+        <v>91277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>128533911</v>
       </c>
       <c r="B7" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,21 +1204,12 @@
       <c r="E7" t="n">
         <v>5449</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128534131</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128533836</v>
       </c>
       <c r="B6" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>128533911</v>
       </c>
       <c r="B7" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128534131</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128533836</v>
       </c>
       <c r="B6" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>128533911</v>
       </c>
       <c r="B7" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128533836</v>
       </c>
       <c r="B6" t="n">
-        <v>91288</v>
+        <v>91293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>128533911</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128534071</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128533836</v>
       </c>
       <c r="B6" t="n">
-        <v>91293</v>
+        <v>91299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>128533911</v>
       </c>
       <c r="B7" t="n">
-        <v>92840</v>
+        <v>92848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128534071</v>
+        <v>128533836</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616851</v>
+        <v>616885</v>
       </c>
       <c r="R2" t="n">
-        <v>6763699</v>
+        <v>6763676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +779,7 @@
         <v>128534053</v>
       </c>
       <c r="B3" t="n">
-        <v>92464</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,11 +880,11 @@
         <v>128534131</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -991,7 +990,7 @@
         <v>128533980</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128533836</v>
+        <v>128534071</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,26 +1100,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616885</v>
+        <v>616851</v>
       </c>
       <c r="R6" t="n">
-        <v>6763676</v>
+        <v>6763699</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,98 +1188,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>128533911</v>
-      </c>
-      <c r="B7" t="n">
-        <v>92848</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5449</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Karlsbäck, Gstr</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>616867</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6763683</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Gävle</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Hamrånge</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34666-2025 artfynd.xlsx
+++ b/artfynd/A 34666-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533836</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128534053</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128534131</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533980</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,8 +1213,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128534071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>